--- a/diabetics-medicines/medicines.xlsx
+++ b/diabetics-medicines/medicines.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -431,21 +431,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:E176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Weekday</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Atorvastatin</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Dapagliflozin</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Metformin</t>
         </is>
@@ -455,11 +465,16 @@
       <c r="A2" s="2" t="n">
         <v>45789</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>540</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
         <v>27500</v>
       </c>
     </row>
@@ -467,11 +482,16 @@
       <c r="A3" s="2" t="n">
         <v>45790</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>520</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
         <v>27000</v>
       </c>
     </row>
@@ -479,11 +499,16 @@
       <c r="A4" s="2" t="n">
         <v>45791</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>500</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
         <v>26500</v>
       </c>
     </row>
@@ -491,11 +516,16 @@
       <c r="A5" s="2" t="n">
         <v>45792</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>480</v>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
         <v>26000</v>
       </c>
     </row>
@@ -503,11 +533,16 @@
       <c r="A6" s="2" t="n">
         <v>45793</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>460</v>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
         <v>25500</v>
       </c>
     </row>
@@ -515,11 +550,16 @@
       <c r="A7" s="2" t="n">
         <v>45794</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>440</v>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
         <v>25000</v>
       </c>
     </row>
@@ -527,11 +567,16 @@
       <c r="A8" s="2" t="n">
         <v>45795</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>420</v>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="n">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
         <v>24500</v>
       </c>
     </row>
@@ -539,11 +584,16 @@
       <c r="A9" s="2" t="n">
         <v>45796</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>400</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="n">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
         <v>23500</v>
       </c>
     </row>
@@ -551,11 +601,16 @@
       <c r="A10" s="2" t="n">
         <v>45797</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>380</v>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="n">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
         <v>22500</v>
       </c>
     </row>
@@ -563,11 +618,16 @@
       <c r="A11" s="2" t="n">
         <v>45798</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>360</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="n">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
         <v>21500</v>
       </c>
     </row>
@@ -575,11 +635,16 @@
       <c r="A12" s="2" t="n">
         <v>45799</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>340</v>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="n">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
         <v>20500</v>
       </c>
     </row>
@@ -587,11 +652,16 @@
       <c r="A13" s="2" t="n">
         <v>45800</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>320</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="n">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -599,11 +669,16 @@
       <c r="A14" s="2" t="n">
         <v>45801</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>300</v>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
         <v>18500</v>
       </c>
     </row>
@@ -611,11 +686,16 @@
       <c r="A15" s="2" t="n">
         <v>45802</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>280</v>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="n">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
         <v>17500</v>
       </c>
     </row>
@@ -623,11 +703,16 @@
       <c r="A16" s="2" t="n">
         <v>45803</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>260</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
         <v>16000</v>
       </c>
     </row>
@@ -635,11 +720,16 @@
       <c r="A17" s="2" t="n">
         <v>45804</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>240</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="n">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
         <v>14500</v>
       </c>
     </row>
@@ -647,11 +737,16 @@
       <c r="A18" s="2" t="n">
         <v>45805</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>220</v>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="n">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
         <v>13000</v>
       </c>
     </row>
@@ -659,11 +754,16 @@
       <c r="A19" s="2" t="n">
         <v>45806</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>200</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="n">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
         <v>11500</v>
       </c>
     </row>
@@ -671,11 +771,16 @@
       <c r="A20" s="2" t="n">
         <v>45807</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>180</v>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="n">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -683,11 +788,16 @@
       <c r="A21" s="2" t="n">
         <v>45808</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>160</v>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="n">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
         <v>8500</v>
       </c>
     </row>
@@ -695,11 +805,16 @@
       <c r="A22" s="2" t="n">
         <v>45809</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>140</v>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="n">
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
         <v>7000</v>
       </c>
     </row>
@@ -707,11 +822,16 @@
       <c r="A23" s="2" t="n">
         <v>45810</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
         <v>120</v>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="n">
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
         <v>5500</v>
       </c>
     </row>
@@ -719,11 +839,16 @@
       <c r="A24" s="2" t="n">
         <v>45811</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>100</v>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="n">
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -731,11 +856,16 @@
       <c r="A25" s="2" t="n">
         <v>45812</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>640</v>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="n">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
         <v>30500</v>
       </c>
     </row>
@@ -743,11 +873,16 @@
       <c r="A26" s="2" t="n">
         <v>45813</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
         <v>620</v>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="n">
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
         <v>29000</v>
       </c>
     </row>
@@ -755,11 +890,16 @@
       <c r="A27" s="2" t="n">
         <v>45814</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
         <v>600</v>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="n">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
         <v>27500</v>
       </c>
     </row>
@@ -767,11 +907,16 @@
       <c r="A28" s="2" t="n">
         <v>45815</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>580</v>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="n">
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
         <v>26000</v>
       </c>
     </row>
@@ -779,11 +924,16 @@
       <c r="A29" s="2" t="n">
         <v>45816</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
         <v>560</v>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="n">
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
         <v>24500</v>
       </c>
     </row>
@@ -791,11 +941,16 @@
       <c r="A30" s="2" t="n">
         <v>45817</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>540</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="n">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
         <v>23000</v>
       </c>
     </row>
@@ -803,11 +958,16 @@
       <c r="A31" s="2" t="n">
         <v>45818</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>520</v>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="n">
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
         <v>21500</v>
       </c>
     </row>
@@ -815,11 +975,16 @@
       <c r="A32" s="2" t="n">
         <v>45819</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
         <v>500</v>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="n">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -827,11 +992,16 @@
       <c r="A33" s="2" t="n">
         <v>45820</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
         <v>480</v>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="n">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
         <v>18500</v>
       </c>
     </row>
@@ -839,11 +1009,16 @@
       <c r="A34" s="2" t="n">
         <v>45821</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
         <v>460</v>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="n">
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
         <v>17000</v>
       </c>
     </row>
@@ -851,11 +1026,16 @@
       <c r="A35" s="2" t="n">
         <v>45822</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
         <v>440</v>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="n">
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
         <v>15500</v>
       </c>
     </row>
@@ -863,11 +1043,16 @@
       <c r="A36" s="2" t="n">
         <v>45823</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
         <v>420</v>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="n">
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
         <v>14000</v>
       </c>
     </row>
@@ -875,11 +1060,16 @@
       <c r="A37" s="2" t="n">
         <v>45824</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>400</v>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="n">
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
         <v>12500</v>
       </c>
     </row>
@@ -887,11 +1077,16 @@
       <c r="A38" s="2" t="n">
         <v>45825</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
         <v>380</v>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="n">
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
         <v>53000</v>
       </c>
     </row>
@@ -899,11 +1094,16 @@
       <c r="A39" s="2" t="n">
         <v>45826</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
         <v>360</v>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="n">
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
         <v>51500</v>
       </c>
     </row>
@@ -911,11 +1111,16 @@
       <c r="A40" s="2" t="n">
         <v>45827</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
         <v>340</v>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="n">
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -923,11 +1128,16 @@
       <c r="A41" s="2" t="n">
         <v>45828</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
         <v>320</v>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="n">
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
         <v>48500</v>
       </c>
     </row>
@@ -935,11 +1145,16 @@
       <c r="A42" s="2" t="n">
         <v>45829</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
         <v>300</v>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="n">
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
         <v>47000</v>
       </c>
     </row>
@@ -947,11 +1162,16 @@
       <c r="A43" s="2" t="n">
         <v>45830</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
         <v>280</v>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="n">
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
         <v>45500</v>
       </c>
     </row>
@@ -959,11 +1179,16 @@
       <c r="A44" s="2" t="n">
         <v>45831</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
         <v>260</v>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="n">
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
         <v>44000</v>
       </c>
     </row>
@@ -971,11 +1196,16 @@
       <c r="A45" s="2" t="n">
         <v>45832</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
         <v>240</v>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="n">
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
         <v>42500</v>
       </c>
     </row>
@@ -983,11 +1213,16 @@
       <c r="A46" s="2" t="n">
         <v>45833</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
         <v>220</v>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="n">
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
         <v>41000</v>
       </c>
     </row>
@@ -995,11 +1230,16 @@
       <c r="A47" s="2" t="n">
         <v>45834</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
         <v>200</v>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="n">
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
         <v>39500</v>
       </c>
     </row>
@@ -1007,11 +1247,16 @@
       <c r="A48" s="2" t="n">
         <v>45835</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
         <v>180</v>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="n">
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
         <v>38000</v>
       </c>
     </row>
@@ -1019,11 +1264,16 @@
       <c r="A49" s="2" t="n">
         <v>45836</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
         <v>160</v>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="n">
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
         <v>36500</v>
       </c>
     </row>
@@ -1031,11 +1281,16 @@
       <c r="A50" s="2" t="n">
         <v>45837</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
         <v>140</v>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="n">
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
         <v>35000</v>
       </c>
     </row>
@@ -1043,11 +1298,16 @@
       <c r="A51" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
         <v>120</v>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="n">
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="n">
         <v>33500</v>
       </c>
     </row>
@@ -1055,13 +1315,18 @@
       <c r="A52" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
         <v>1200</v>
       </c>
-      <c r="C52" t="n">
+      <c r="D52" t="n">
         <v>135</v>
       </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
         <v>87500</v>
       </c>
     </row>
@@ -1069,13 +1334,18 @@
       <c r="A53" s="2" t="n">
         <v>45840</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
         <v>1160</v>
       </c>
-      <c r="C53" t="n">
+      <c r="D53" t="n">
         <v>130</v>
       </c>
-      <c r="D53" t="n">
+      <c r="E53" t="n">
         <v>85500</v>
       </c>
     </row>
@@ -1083,13 +1353,18 @@
       <c r="A54" s="2" t="n">
         <v>45841</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
         <v>1120</v>
       </c>
-      <c r="C54" t="n">
+      <c r="D54" t="n">
         <v>125</v>
       </c>
-      <c r="D54" t="n">
+      <c r="E54" t="n">
         <v>83500</v>
       </c>
     </row>
@@ -1097,13 +1372,18 @@
       <c r="A55" s="2" t="n">
         <v>45842</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
         <v>1080</v>
       </c>
-      <c r="C55" t="n">
+      <c r="D55" t="n">
         <v>120</v>
       </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
         <v>81500</v>
       </c>
     </row>
@@ -1111,13 +1391,18 @@
       <c r="A56" s="2" t="n">
         <v>45843</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
         <v>1040</v>
       </c>
-      <c r="C56" t="n">
+      <c r="D56" t="n">
         <v>115</v>
       </c>
-      <c r="D56" t="n">
+      <c r="E56" t="n">
         <v>79500</v>
       </c>
     </row>
@@ -1125,13 +1410,18 @@
       <c r="A57" s="2" t="n">
         <v>45844</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
         <v>1000</v>
       </c>
-      <c r="C57" t="n">
+      <c r="D57" t="n">
         <v>110</v>
       </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
         <v>77500</v>
       </c>
     </row>
@@ -1139,13 +1429,18 @@
       <c r="A58" s="2" t="n">
         <v>45845</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
         <v>960</v>
       </c>
-      <c r="C58" t="n">
+      <c r="D58" t="n">
         <v>105</v>
       </c>
-      <c r="D58" t="n">
+      <c r="E58" t="n">
         <v>75500</v>
       </c>
     </row>
@@ -1153,13 +1448,18 @@
       <c r="A59" s="2" t="n">
         <v>45846</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
         <v>920</v>
       </c>
-      <c r="C59" t="n">
+      <c r="D59" t="n">
         <v>100</v>
       </c>
-      <c r="D59" t="n">
+      <c r="E59" t="n">
         <v>73500</v>
       </c>
     </row>
@@ -1167,13 +1467,18 @@
       <c r="A60" s="2" t="n">
         <v>45847</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
         <v>880</v>
       </c>
-      <c r="C60" t="n">
+      <c r="D60" t="n">
         <v>95</v>
       </c>
-      <c r="D60" t="n">
+      <c r="E60" t="n">
         <v>71500</v>
       </c>
     </row>
@@ -1181,13 +1486,18 @@
       <c r="A61" s="2" t="n">
         <v>45848</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
         <v>840</v>
       </c>
-      <c r="C61" t="n">
+      <c r="D61" t="n">
         <v>90</v>
       </c>
-      <c r="D61" t="n">
+      <c r="E61" t="n">
         <v>69500</v>
       </c>
     </row>
@@ -1195,13 +1505,18 @@
       <c r="A62" s="2" t="n">
         <v>45849</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
         <v>800</v>
       </c>
-      <c r="C62" t="n">
+      <c r="D62" t="n">
         <v>85</v>
       </c>
-      <c r="D62" t="n">
+      <c r="E62" t="n">
         <v>67500</v>
       </c>
     </row>
@@ -1209,13 +1524,18 @@
       <c r="A63" s="2" t="n">
         <v>45850</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
         <v>760</v>
       </c>
-      <c r="C63" t="n">
+      <c r="D63" t="n">
         <v>80</v>
       </c>
-      <c r="D63" t="n">
+      <c r="E63" t="n">
         <v>65500</v>
       </c>
     </row>
@@ -1223,13 +1543,18 @@
       <c r="A64" s="2" t="n">
         <v>45851</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
         <v>720</v>
       </c>
-      <c r="C64" t="n">
+      <c r="D64" t="n">
         <v>75</v>
       </c>
-      <c r="D64" t="n">
+      <c r="E64" t="n">
         <v>63500</v>
       </c>
     </row>
@@ -1237,13 +1562,18 @@
       <c r="A65" s="2" t="n">
         <v>45852</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
         <v>680</v>
       </c>
-      <c r="C65" t="n">
+      <c r="D65" t="n">
         <v>70</v>
       </c>
-      <c r="D65" t="n">
+      <c r="E65" t="n">
         <v>61500</v>
       </c>
     </row>
@@ -1251,13 +1581,18 @@
       <c r="A66" s="2" t="n">
         <v>45853</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
         <v>640</v>
       </c>
-      <c r="C66" t="n">
+      <c r="D66" t="n">
         <v>65</v>
       </c>
-      <c r="D66" t="n">
+      <c r="E66" t="n">
         <v>59500</v>
       </c>
     </row>
@@ -1265,13 +1600,18 @@
       <c r="A67" s="2" t="n">
         <v>45854</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
         <v>600</v>
       </c>
-      <c r="C67" t="n">
+      <c r="D67" t="n">
         <v>60</v>
       </c>
-      <c r="D67" t="n">
+      <c r="E67" t="n">
         <v>57500</v>
       </c>
     </row>
@@ -1279,13 +1619,18 @@
       <c r="A68" s="2" t="n">
         <v>45855</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
         <v>560</v>
       </c>
-      <c r="C68" t="n">
+      <c r="D68" t="n">
         <v>55</v>
       </c>
-      <c r="D68" t="n">
+      <c r="E68" t="n">
         <v>55500</v>
       </c>
     </row>
@@ -1293,13 +1638,18 @@
       <c r="A69" s="2" t="n">
         <v>45856</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
         <v>520</v>
       </c>
-      <c r="C69" t="n">
+      <c r="D69" t="n">
         <v>50</v>
       </c>
-      <c r="D69" t="n">
+      <c r="E69" t="n">
         <v>53500</v>
       </c>
     </row>
@@ -1307,13 +1657,18 @@
       <c r="A70" s="2" t="n">
         <v>45857</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
         <v>480</v>
       </c>
-      <c r="C70" t="n">
+      <c r="D70" t="n">
         <v>45</v>
       </c>
-      <c r="D70" t="n">
+      <c r="E70" t="n">
         <v>51500</v>
       </c>
     </row>
@@ -1321,13 +1676,18 @@
       <c r="A71" s="2" t="n">
         <v>45858</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
         <v>440</v>
       </c>
-      <c r="C71" t="n">
+      <c r="D71" t="n">
         <v>40</v>
       </c>
-      <c r="D71" t="n">
+      <c r="E71" t="n">
         <v>49500</v>
       </c>
     </row>
@@ -1335,13 +1695,18 @@
       <c r="A72" s="2" t="n">
         <v>45859</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
         <v>400</v>
       </c>
-      <c r="C72" t="n">
+      <c r="D72" t="n">
         <v>35</v>
       </c>
-      <c r="D72" t="n">
+      <c r="E72" t="n">
         <v>47500</v>
       </c>
     </row>
@@ -1349,13 +1714,18 @@
       <c r="A73" s="2" t="n">
         <v>45860</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
         <v>360</v>
       </c>
-      <c r="C73" t="n">
+      <c r="D73" t="n">
         <v>30</v>
       </c>
-      <c r="D73" t="n">
+      <c r="E73" t="n">
         <v>45500</v>
       </c>
     </row>
@@ -1363,13 +1733,18 @@
       <c r="A74" s="2" t="n">
         <v>45861</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
         <v>1440</v>
       </c>
-      <c r="C74" t="n">
+      <c r="D74" t="n">
         <v>165</v>
       </c>
-      <c r="D74" t="n">
+      <c r="E74" t="n">
         <v>43500</v>
       </c>
     </row>
@@ -1377,13 +1752,18 @@
       <c r="A75" s="2" t="n">
         <v>45862</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
         <v>1400</v>
       </c>
-      <c r="C75" t="n">
+      <c r="D75" t="n">
         <v>160</v>
       </c>
-      <c r="D75" t="n">
+      <c r="E75" t="n">
         <v>41500</v>
       </c>
     </row>
@@ -1391,13 +1771,18 @@
       <c r="A76" s="2" t="n">
         <v>45863</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
         <v>1360</v>
       </c>
-      <c r="C76" t="n">
+      <c r="D76" t="n">
         <v>155</v>
       </c>
-      <c r="D76" t="n">
+      <c r="E76" t="n">
         <v>39500</v>
       </c>
     </row>
@@ -1405,13 +1790,18 @@
       <c r="A77" s="2" t="n">
         <v>45864</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
         <v>1320</v>
       </c>
-      <c r="C77" t="n">
+      <c r="D77" t="n">
         <v>150</v>
       </c>
-      <c r="D77" t="n">
+      <c r="E77" t="n">
         <v>37500</v>
       </c>
     </row>
@@ -1419,13 +1809,18 @@
       <c r="A78" s="2" t="n">
         <v>45865</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
         <v>1280</v>
       </c>
-      <c r="C78" t="n">
+      <c r="D78" t="n">
         <v>145</v>
       </c>
-      <c r="D78" t="n">
+      <c r="E78" t="n">
         <v>35500</v>
       </c>
     </row>
@@ -1433,13 +1828,18 @@
       <c r="A79" s="2" t="n">
         <v>45866</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
         <v>1240</v>
       </c>
-      <c r="C79" t="n">
+      <c r="D79" t="n">
         <v>140</v>
       </c>
-      <c r="D79" t="n">
+      <c r="E79" t="n">
         <v>33500</v>
       </c>
     </row>
@@ -1447,13 +1847,18 @@
       <c r="A80" s="2" t="n">
         <v>45867</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
         <v>1200</v>
       </c>
-      <c r="C80" t="n">
+      <c r="D80" t="n">
         <v>135</v>
       </c>
-      <c r="D80" t="n">
+      <c r="E80" t="n">
         <v>31500</v>
       </c>
     </row>
@@ -1461,13 +1866,18 @@
       <c r="A81" s="2" t="n">
         <v>45868</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
         <v>1160</v>
       </c>
-      <c r="C81" t="n">
+      <c r="D81" t="n">
         <v>130</v>
       </c>
-      <c r="D81" t="n">
+      <c r="E81" t="n">
         <v>29500</v>
       </c>
     </row>
@@ -1475,13 +1885,18 @@
       <c r="A82" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
         <v>1120</v>
       </c>
-      <c r="C82" t="n">
+      <c r="D82" t="n">
         <v>125</v>
       </c>
-      <c r="D82" t="n">
+      <c r="E82" t="n">
         <v>27500</v>
       </c>
     </row>
@@ -1489,13 +1904,18 @@
       <c r="A83" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
         <v>1080</v>
       </c>
-      <c r="C83" t="n">
+      <c r="D83" t="n">
         <v>120</v>
       </c>
-      <c r="D83" t="n">
+      <c r="E83" t="n">
         <v>25500</v>
       </c>
     </row>
@@ -1503,13 +1923,18 @@
       <c r="A84" s="2" t="n">
         <v>45871</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
         <v>1040</v>
       </c>
-      <c r="C84" t="n">
+      <c r="D84" t="n">
         <v>115</v>
       </c>
-      <c r="D84" t="n">
+      <c r="E84" t="n">
         <v>23500</v>
       </c>
     </row>
@@ -1517,13 +1942,18 @@
       <c r="A85" s="2" t="n">
         <v>45872</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
         <v>1000</v>
       </c>
-      <c r="C85" t="n">
+      <c r="D85" t="n">
         <v>110</v>
       </c>
-      <c r="D85" t="n">
+      <c r="E85" t="n">
         <v>21500</v>
       </c>
     </row>
@@ -1531,13 +1961,18 @@
       <c r="A86" s="2" t="n">
         <v>45873</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
         <v>960</v>
       </c>
-      <c r="C86" t="n">
+      <c r="D86" t="n">
         <v>105</v>
       </c>
-      <c r="D86" t="n">
+      <c r="E86" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -1545,13 +1980,18 @@
       <c r="A87" s="2" t="n">
         <v>45874</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
         <v>920</v>
       </c>
-      <c r="C87" t="n">
+      <c r="D87" t="n">
         <v>100</v>
       </c>
-      <c r="D87" t="n">
+      <c r="E87" t="n">
         <v>17500</v>
       </c>
     </row>
@@ -1559,13 +1999,18 @@
       <c r="A88" s="2" t="n">
         <v>45875</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
         <v>880</v>
       </c>
-      <c r="C88" t="n">
+      <c r="D88" t="n">
         <v>95</v>
       </c>
-      <c r="D88" t="n">
+      <c r="E88" t="n">
         <v>15500</v>
       </c>
     </row>
@@ -1573,13 +2018,18 @@
       <c r="A89" s="2" t="n">
         <v>45876</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
         <v>840</v>
       </c>
-      <c r="C89" t="n">
+      <c r="D89" t="n">
         <v>90</v>
       </c>
-      <c r="D89" t="n">
+      <c r="E89" t="n">
         <v>13500</v>
       </c>
     </row>
@@ -1587,13 +2037,18 @@
       <c r="A90" s="2" t="n">
         <v>45877</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
         <v>800</v>
       </c>
-      <c r="C90" t="n">
+      <c r="D90" t="n">
         <v>85</v>
       </c>
-      <c r="D90" t="n">
+      <c r="E90" t="n">
         <v>67500</v>
       </c>
     </row>
@@ -1601,13 +2056,18 @@
       <c r="A91" s="2" t="n">
         <v>45878</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
         <v>760</v>
       </c>
-      <c r="C91" t="n">
+      <c r="D91" t="n">
         <v>80</v>
       </c>
-      <c r="D91" t="n">
+      <c r="E91" t="n">
         <v>65500</v>
       </c>
     </row>
@@ -1615,13 +2075,18 @@
       <c r="A92" s="2" t="n">
         <v>45879</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
         <v>720</v>
       </c>
-      <c r="C92" t="n">
+      <c r="D92" t="n">
         <v>75</v>
       </c>
-      <c r="D92" t="n">
+      <c r="E92" t="n">
         <v>63500</v>
       </c>
     </row>
@@ -1629,13 +2094,18 @@
       <c r="A93" s="2" t="n">
         <v>45880</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
         <v>680</v>
       </c>
-      <c r="C93" t="n">
+      <c r="D93" t="n">
         <v>70</v>
       </c>
-      <c r="D93" t="n">
+      <c r="E93" t="n">
         <v>61500</v>
       </c>
     </row>
@@ -1643,13 +2113,18 @@
       <c r="A94" s="2" t="n">
         <v>45881</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
         <v>640</v>
       </c>
-      <c r="C94" t="n">
+      <c r="D94" t="n">
         <v>65</v>
       </c>
-      <c r="D94" t="n">
+      <c r="E94" t="n">
         <v>59500</v>
       </c>
     </row>
@@ -1657,13 +2132,18 @@
       <c r="A95" s="2" t="n">
         <v>45882</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
         <v>600</v>
       </c>
-      <c r="C95" t="n">
+      <c r="D95" t="n">
         <v>60</v>
       </c>
-      <c r="D95" t="n">
+      <c r="E95" t="n">
         <v>57500</v>
       </c>
     </row>
@@ -1671,13 +2151,18 @@
       <c r="A96" s="2" t="n">
         <v>45883</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
         <v>560</v>
       </c>
-      <c r="C96" t="n">
+      <c r="D96" t="n">
         <v>55</v>
       </c>
-      <c r="D96" t="n">
+      <c r="E96" t="n">
         <v>55500</v>
       </c>
     </row>
@@ -1685,13 +2170,18 @@
       <c r="A97" s="2" t="n">
         <v>45884</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
         <v>520</v>
       </c>
-      <c r="C97" t="n">
+      <c r="D97" t="n">
         <v>50</v>
       </c>
-      <c r="D97" t="n">
+      <c r="E97" t="n">
         <v>53500</v>
       </c>
     </row>
@@ -1699,13 +2189,18 @@
       <c r="A98" s="2" t="n">
         <v>45885</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
         <v>480</v>
       </c>
-      <c r="C98" t="n">
+      <c r="D98" t="n">
         <v>45</v>
       </c>
-      <c r="D98" t="n">
+      <c r="E98" t="n">
         <v>51500</v>
       </c>
     </row>
@@ -1713,13 +2208,18 @@
       <c r="A99" s="2" t="n">
         <v>45886</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
         <v>440</v>
       </c>
-      <c r="C99" t="n">
+      <c r="D99" t="n">
         <v>40</v>
       </c>
-      <c r="D99" t="n">
+      <c r="E99" t="n">
         <v>49500</v>
       </c>
     </row>
@@ -1727,13 +2227,18 @@
       <c r="A100" s="2" t="n">
         <v>45887</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
         <v>400</v>
       </c>
-      <c r="C100" t="n">
+      <c r="D100" t="n">
         <v>35</v>
       </c>
-      <c r="D100" t="n">
+      <c r="E100" t="n">
         <v>47500</v>
       </c>
     </row>
@@ -1741,13 +2246,18 @@
       <c r="A101" s="2" t="n">
         <v>45888</v>
       </c>
-      <c r="B101" t="n">
-        <v>360</v>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
       </c>
       <c r="C101" t="n">
-        <v>30</v>
+        <v>1480</v>
       </c>
       <c r="D101" t="n">
+        <v>170</v>
+      </c>
+      <c r="E101" t="n">
         <v>45500</v>
       </c>
     </row>
@@ -1755,13 +2265,18 @@
       <c r="A102" s="2" t="n">
         <v>45889</v>
       </c>
-      <c r="B102" t="n">
-        <v>320</v>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
       </c>
       <c r="C102" t="n">
-        <v>25</v>
+        <v>1440</v>
       </c>
       <c r="D102" t="n">
+        <v>165</v>
+      </c>
+      <c r="E102" t="n">
         <v>43500</v>
       </c>
     </row>
@@ -1769,13 +2284,18 @@
       <c r="A103" s="2" t="n">
         <v>45890</v>
       </c>
-      <c r="B103" t="n">
-        <v>280</v>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
       </c>
       <c r="C103" t="n">
-        <v>20</v>
+        <v>1400</v>
       </c>
       <c r="D103" t="n">
+        <v>160</v>
+      </c>
+      <c r="E103" t="n">
         <v>41500</v>
       </c>
     </row>
@@ -1783,13 +2303,18 @@
       <c r="A104" s="2" t="n">
         <v>45891</v>
       </c>
-      <c r="B104" t="n">
-        <v>240</v>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
       </c>
       <c r="C104" t="n">
-        <v>15</v>
+        <v>1360</v>
       </c>
       <c r="D104" t="n">
+        <v>155</v>
+      </c>
+      <c r="E104" t="n">
         <v>39500</v>
       </c>
     </row>
@@ -1797,13 +2322,18 @@
       <c r="A105" s="2" t="n">
         <v>45892</v>
       </c>
-      <c r="B105" t="n">
-        <v>200</v>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
       </c>
       <c r="C105" t="n">
-        <v>10</v>
+        <v>1320</v>
       </c>
       <c r="D105" t="n">
+        <v>150</v>
+      </c>
+      <c r="E105" t="n">
         <v>37500</v>
       </c>
     </row>
@@ -1811,13 +2341,18 @@
       <c r="A106" s="2" t="n">
         <v>45893</v>
       </c>
-      <c r="B106" t="n">
-        <v>160</v>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
       </c>
       <c r="C106" t="n">
-        <v>5</v>
+        <v>1280</v>
       </c>
       <c r="D106" t="n">
+        <v>145</v>
+      </c>
+      <c r="E106" t="n">
         <v>35500</v>
       </c>
     </row>
@@ -1825,125 +2360,170 @@
       <c r="A107" s="2" t="n">
         <v>45894</v>
       </c>
-      <c r="B107" t="n">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
         <v>1240</v>
       </c>
-      <c r="C107" t="n">
+      <c r="D107" t="n">
         <v>140</v>
       </c>
-      <c r="D107" t="n">
-        <v>89500</v>
+      <c r="E107" t="n">
+        <v>33500</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
         <v>45895</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
         <v>1200</v>
       </c>
-      <c r="C108" t="n">
+      <c r="D108" t="n">
         <v>135</v>
       </c>
-      <c r="D108" t="n">
-        <v>87500</v>
+      <c r="E108" t="n">
+        <v>31500</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
         <v>45896</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
         <v>1160</v>
       </c>
-      <c r="C109" t="n">
+      <c r="D109" t="n">
         <v>130</v>
       </c>
-      <c r="D109" t="n">
-        <v>85500</v>
+      <c r="E109" t="n">
+        <v>29500</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
         <v>45897</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
         <v>1120</v>
       </c>
-      <c r="C110" t="n">
+      <c r="D110" t="n">
         <v>125</v>
       </c>
-      <c r="D110" t="n">
-        <v>83500</v>
+      <c r="E110" t="n">
+        <v>27500</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
         <v>45898</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
         <v>1080</v>
       </c>
-      <c r="C111" t="n">
+      <c r="D111" t="n">
         <v>120</v>
       </c>
-      <c r="D111" t="n">
-        <v>81500</v>
+      <c r="E111" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
         <v>45899</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
         <v>1040</v>
       </c>
-      <c r="C112" t="n">
+      <c r="D112" t="n">
         <v>115</v>
       </c>
-      <c r="D112" t="n">
-        <v>79500</v>
+      <c r="E112" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
         <v>45900</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
         <v>1000</v>
       </c>
-      <c r="C113" t="n">
+      <c r="D113" t="n">
         <v>110</v>
       </c>
-      <c r="D113" t="n">
-        <v>77500</v>
+      <c r="E113" t="n">
+        <v>21500</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
         <v>45901</v>
       </c>
-      <c r="B114" t="n">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
         <v>960</v>
       </c>
-      <c r="C114" t="n">
+      <c r="D114" t="n">
         <v>105</v>
       </c>
-      <c r="D114" t="n">
-        <v>75500</v>
+      <c r="E114" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
         <v>45902</v>
       </c>
-      <c r="B115" t="n">
-        <v>920</v>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
       </c>
       <c r="C115" t="n">
-        <v>100</v>
+        <v>2040</v>
       </c>
       <c r="D115" t="n">
+        <v>240</v>
+      </c>
+      <c r="E115" t="n">
         <v>73500</v>
       </c>
     </row>
@@ -1951,13 +2531,18 @@
       <c r="A116" s="2" t="n">
         <v>45903</v>
       </c>
-      <c r="B116" t="n">
-        <v>880</v>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
       </c>
       <c r="C116" t="n">
-        <v>95</v>
+        <v>2000</v>
       </c>
       <c r="D116" t="n">
+        <v>235</v>
+      </c>
+      <c r="E116" t="n">
         <v>71500</v>
       </c>
     </row>
@@ -1965,13 +2550,18 @@
       <c r="A117" s="2" t="n">
         <v>45904</v>
       </c>
-      <c r="B117" t="n">
-        <v>840</v>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
       </c>
       <c r="C117" t="n">
-        <v>90</v>
+        <v>1960</v>
       </c>
       <c r="D117" t="n">
+        <v>230</v>
+      </c>
+      <c r="E117" t="n">
         <v>69500</v>
       </c>
     </row>
@@ -1979,13 +2569,18 @@
       <c r="A118" s="2" t="n">
         <v>45905</v>
       </c>
-      <c r="B118" t="n">
-        <v>800</v>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
       </c>
       <c r="C118" t="n">
-        <v>85</v>
+        <v>1920</v>
       </c>
       <c r="D118" t="n">
+        <v>225</v>
+      </c>
+      <c r="E118" t="n">
         <v>67500</v>
       </c>
     </row>
@@ -1993,13 +2588,18 @@
       <c r="A119" s="2" t="n">
         <v>45906</v>
       </c>
-      <c r="B119" t="n">
-        <v>760</v>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
       </c>
       <c r="C119" t="n">
-        <v>80</v>
+        <v>1880</v>
       </c>
       <c r="D119" t="n">
+        <v>220</v>
+      </c>
+      <c r="E119" t="n">
         <v>65500</v>
       </c>
     </row>
@@ -2007,13 +2607,18 @@
       <c r="A120" s="2" t="n">
         <v>45907</v>
       </c>
-      <c r="B120" t="n">
-        <v>720</v>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
       </c>
       <c r="C120" t="n">
-        <v>75</v>
+        <v>1840</v>
       </c>
       <c r="D120" t="n">
+        <v>215</v>
+      </c>
+      <c r="E120" t="n">
         <v>63500</v>
       </c>
     </row>
@@ -2021,13 +2626,18 @@
       <c r="A121" s="2" t="n">
         <v>45908</v>
       </c>
-      <c r="B121" t="n">
-        <v>680</v>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
       </c>
       <c r="C121" t="n">
-        <v>70</v>
+        <v>1800</v>
       </c>
       <c r="D121" t="n">
+        <v>210</v>
+      </c>
+      <c r="E121" t="n">
         <v>61500</v>
       </c>
     </row>
@@ -2035,13 +2645,18 @@
       <c r="A122" s="2" t="n">
         <v>45909</v>
       </c>
-      <c r="B122" t="n">
-        <v>640</v>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
       </c>
       <c r="C122" t="n">
-        <v>65</v>
+        <v>1760</v>
       </c>
       <c r="D122" t="n">
+        <v>205</v>
+      </c>
+      <c r="E122" t="n">
         <v>59500</v>
       </c>
     </row>
@@ -2049,13 +2664,18 @@
       <c r="A123" s="2" t="n">
         <v>45910</v>
       </c>
-      <c r="B123" t="n">
-        <v>600</v>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
       </c>
       <c r="C123" t="n">
-        <v>60</v>
+        <v>1720</v>
       </c>
       <c r="D123" t="n">
+        <v>200</v>
+      </c>
+      <c r="E123" t="n">
         <v>57500</v>
       </c>
     </row>
@@ -2063,13 +2683,18 @@
       <c r="A124" s="2" t="n">
         <v>45911</v>
       </c>
-      <c r="B124" t="n">
-        <v>560</v>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
       </c>
       <c r="C124" t="n">
-        <v>55</v>
+        <v>1680</v>
       </c>
       <c r="D124" t="n">
+        <v>195</v>
+      </c>
+      <c r="E124" t="n">
         <v>55500</v>
       </c>
     </row>
@@ -2077,13 +2702,18 @@
       <c r="A125" s="2" t="n">
         <v>45912</v>
       </c>
-      <c r="B125" t="n">
-        <v>520</v>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
       </c>
       <c r="C125" t="n">
-        <v>50</v>
+        <v>1640</v>
       </c>
       <c r="D125" t="n">
+        <v>190</v>
+      </c>
+      <c r="E125" t="n">
         <v>53500</v>
       </c>
     </row>
@@ -2091,13 +2721,18 @@
       <c r="A126" s="2" t="n">
         <v>45913</v>
       </c>
-      <c r="B126" t="n">
-        <v>480</v>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
       </c>
       <c r="C126" t="n">
-        <v>45</v>
+        <v>1600</v>
       </c>
       <c r="D126" t="n">
+        <v>185</v>
+      </c>
+      <c r="E126" t="n">
         <v>51500</v>
       </c>
     </row>
@@ -2105,13 +2740,18 @@
       <c r="A127" s="2" t="n">
         <v>45914</v>
       </c>
-      <c r="B127" t="n">
-        <v>440</v>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
       </c>
       <c r="C127" t="n">
-        <v>40</v>
+        <v>1560</v>
       </c>
       <c r="D127" t="n">
+        <v>180</v>
+      </c>
+      <c r="E127" t="n">
         <v>49500</v>
       </c>
     </row>
@@ -2119,13 +2759,18 @@
       <c r="A128" s="2" t="n">
         <v>45915</v>
       </c>
-      <c r="B128" t="n">
-        <v>400</v>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
       </c>
       <c r="C128" t="n">
-        <v>35</v>
+        <v>1520</v>
       </c>
       <c r="D128" t="n">
+        <v>175</v>
+      </c>
+      <c r="E128" t="n">
         <v>47500</v>
       </c>
     </row>
@@ -2133,13 +2778,18 @@
       <c r="A129" s="2" t="n">
         <v>45916</v>
       </c>
-      <c r="B129" t="n">
-        <v>360</v>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
       </c>
       <c r="C129" t="n">
-        <v>30</v>
+        <v>1480</v>
       </c>
       <c r="D129" t="n">
+        <v>170</v>
+      </c>
+      <c r="E129" t="n">
         <v>45500</v>
       </c>
     </row>
@@ -2147,13 +2797,18 @@
       <c r="A130" s="2" t="n">
         <v>45917</v>
       </c>
-      <c r="B130" t="n">
-        <v>320</v>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
       </c>
       <c r="C130" t="n">
-        <v>25</v>
+        <v>1440</v>
       </c>
       <c r="D130" t="n">
+        <v>165</v>
+      </c>
+      <c r="E130" t="n">
         <v>43500</v>
       </c>
     </row>
@@ -2161,13 +2816,18 @@
       <c r="A131" s="2" t="n">
         <v>45918</v>
       </c>
-      <c r="B131" t="n">
-        <v>280</v>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
       </c>
       <c r="C131" t="n">
-        <v>20</v>
+        <v>1400</v>
       </c>
       <c r="D131" t="n">
+        <v>160</v>
+      </c>
+      <c r="E131" t="n">
         <v>41500</v>
       </c>
     </row>
@@ -2175,13 +2835,18 @@
       <c r="A132" s="2" t="n">
         <v>45919</v>
       </c>
-      <c r="B132" t="n">
-        <v>240</v>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
       </c>
       <c r="C132" t="n">
-        <v>15</v>
+        <v>1360</v>
       </c>
       <c r="D132" t="n">
+        <v>155</v>
+      </c>
+      <c r="E132" t="n">
         <v>39500</v>
       </c>
     </row>
@@ -2189,13 +2854,18 @@
       <c r="A133" s="2" t="n">
         <v>45920</v>
       </c>
-      <c r="B133" t="n">
-        <v>200</v>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
       </c>
       <c r="C133" t="n">
-        <v>10</v>
+        <v>1320</v>
       </c>
       <c r="D133" t="n">
+        <v>150</v>
+      </c>
+      <c r="E133" t="n">
         <v>37500</v>
       </c>
     </row>
@@ -2203,13 +2873,18 @@
       <c r="A134" s="2" t="n">
         <v>45921</v>
       </c>
-      <c r="B134" t="n">
-        <v>160</v>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>1280</v>
       </c>
       <c r="D134" t="n">
+        <v>145</v>
+      </c>
+      <c r="E134" t="n">
         <v>35500</v>
       </c>
     </row>
@@ -2217,11 +2892,18 @@
       <c r="A135" s="2" t="n">
         <v>45922</v>
       </c>
-      <c r="B135" t="n">
-        <v>120</v>
-      </c>
-      <c r="C135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1240</v>
+      </c>
       <c r="D135" t="n">
+        <v>140</v>
+      </c>
+      <c r="E135" t="n">
         <v>33500</v>
       </c>
     </row>
@@ -2229,11 +2911,18 @@
       <c r="A136" s="2" t="n">
         <v>45923</v>
       </c>
-      <c r="B136" t="n">
-        <v>80</v>
-      </c>
-      <c r="C136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1200</v>
+      </c>
       <c r="D136" t="n">
+        <v>135</v>
+      </c>
+      <c r="E136" t="n">
         <v>31500</v>
       </c>
     </row>
@@ -2241,11 +2930,18 @@
       <c r="A137" s="2" t="n">
         <v>45924</v>
       </c>
-      <c r="B137" t="n">
-        <v>40</v>
-      </c>
-      <c r="C137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1160</v>
+      </c>
       <c r="D137" t="n">
+        <v>130</v>
+      </c>
+      <c r="E137" t="n">
         <v>29500</v>
       </c>
     </row>
@@ -2253,9 +2949,18 @@
       <c r="A138" s="2" t="n">
         <v>45925</v>
       </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1120</v>
+      </c>
       <c r="D138" t="n">
+        <v>125</v>
+      </c>
+      <c r="E138" t="n">
         <v>27500</v>
       </c>
     </row>
@@ -2263,9 +2968,18 @@
       <c r="A139" s="2" t="n">
         <v>45926</v>
       </c>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1080</v>
+      </c>
       <c r="D139" t="n">
+        <v>120</v>
+      </c>
+      <c r="E139" t="n">
         <v>25500</v>
       </c>
     </row>
@@ -2273,9 +2987,18 @@
       <c r="A140" s="2" t="n">
         <v>45927</v>
       </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1040</v>
+      </c>
       <c r="D140" t="n">
+        <v>115</v>
+      </c>
+      <c r="E140" t="n">
         <v>23500</v>
       </c>
     </row>
@@ -2283,9 +3006,18 @@
       <c r="A141" s="2" t="n">
         <v>45928</v>
       </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1000</v>
+      </c>
       <c r="D141" t="n">
+        <v>110</v>
+      </c>
+      <c r="E141" t="n">
         <v>21500</v>
       </c>
     </row>
@@ -2293,9 +3025,18 @@
       <c r="A142" s="2" t="n">
         <v>45929</v>
       </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>960</v>
+      </c>
       <c r="D142" t="n">
+        <v>105</v>
+      </c>
+      <c r="E142" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -2303,9 +3044,18 @@
       <c r="A143" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>920</v>
+      </c>
       <c r="D143" t="n">
+        <v>100</v>
+      </c>
+      <c r="E143" t="n">
         <v>17500</v>
       </c>
     </row>
@@ -2313,9 +3063,18 @@
       <c r="A144" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>880</v>
+      </c>
       <c r="D144" t="n">
+        <v>95</v>
+      </c>
+      <c r="E144" t="n">
         <v>15500</v>
       </c>
     </row>
@@ -2323,9 +3082,18 @@
       <c r="A145" s="2" t="n">
         <v>45932</v>
       </c>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>840</v>
+      </c>
       <c r="D145" t="n">
+        <v>90</v>
+      </c>
+      <c r="E145" t="n">
         <v>13500</v>
       </c>
     </row>
@@ -2333,9 +3101,18 @@
       <c r="A146" s="2" t="n">
         <v>45933</v>
       </c>
-      <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>800</v>
+      </c>
       <c r="D146" t="n">
+        <v>85</v>
+      </c>
+      <c r="E146" t="n">
         <v>11500</v>
       </c>
     </row>
@@ -2343,9 +3120,18 @@
       <c r="A147" s="2" t="n">
         <v>45934</v>
       </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>760</v>
+      </c>
       <c r="D147" t="n">
+        <v>80</v>
+      </c>
+      <c r="E147" t="n">
         <v>9500</v>
       </c>
     </row>
@@ -2353,9 +3139,18 @@
       <c r="A148" s="2" t="n">
         <v>45935</v>
       </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>720</v>
+      </c>
       <c r="D148" t="n">
+        <v>75</v>
+      </c>
+      <c r="E148" t="n">
         <v>7500</v>
       </c>
     </row>
@@ -2363,9 +3158,18 @@
       <c r="A149" s="2" t="n">
         <v>45936</v>
       </c>
-      <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>680</v>
+      </c>
       <c r="D149" t="n">
+        <v>70</v>
+      </c>
+      <c r="E149" t="n">
         <v>5500</v>
       </c>
     </row>
@@ -2373,9 +3177,18 @@
       <c r="A150" s="2" t="n">
         <v>45937</v>
       </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>640</v>
+      </c>
       <c r="D150" t="n">
+        <v>65</v>
+      </c>
+      <c r="E150" t="n">
         <v>3500</v>
       </c>
     </row>
@@ -2383,11 +3196,395 @@
       <c r="A151" s="2" t="n">
         <v>45938</v>
       </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>600</v>
+      </c>
       <c r="D151" t="n">
+        <v>60</v>
+      </c>
+      <c r="E151" t="n">
         <v>1500</v>
       </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>560</v>
+      </c>
+      <c r="D152" t="n">
+        <v>55</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>520</v>
+      </c>
+      <c r="D153" t="n">
+        <v>50</v>
+      </c>
+      <c r="E153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>480</v>
+      </c>
+      <c r="D154" t="n">
+        <v>45</v>
+      </c>
+      <c r="E154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>45942</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>440</v>
+      </c>
+      <c r="D155" t="n">
+        <v>40</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>400</v>
+      </c>
+      <c r="D156" t="n">
+        <v>35</v>
+      </c>
+      <c r="E156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>360</v>
+      </c>
+      <c r="D157" t="n">
+        <v>30</v>
+      </c>
+      <c r="E157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>320</v>
+      </c>
+      <c r="D158" t="n">
+        <v>25</v>
+      </c>
+      <c r="E158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>280</v>
+      </c>
+      <c r="D159" t="n">
+        <v>20</v>
+      </c>
+      <c r="E159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>240</v>
+      </c>
+      <c r="D160" t="n">
+        <v>15</v>
+      </c>
+      <c r="E160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>45948</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>200</v>
+      </c>
+      <c r="D161" t="n">
+        <v>10</v>
+      </c>
+      <c r="E161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>45949</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>160</v>
+      </c>
+      <c r="D162" t="n">
+        <v>5</v>
+      </c>
+      <c r="E162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>120</v>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>80</v>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>40</v>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>45956</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>45963</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Sunday - for nan (mg):</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/diabetics-medicines/medicines.xlsx
+++ b/diabetics-medicines/medicines.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E176"/>
+  <dimension ref="A1:E285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3075,7 +3075,7 @@
         <v>95</v>
       </c>
       <c r="E144" t="n">
-        <v>15500</v>
+        <v>71500</v>
       </c>
     </row>
     <row r="145">
@@ -3094,7 +3094,7 @@
         <v>90</v>
       </c>
       <c r="E145" t="n">
-        <v>13500</v>
+        <v>69500</v>
       </c>
     </row>
     <row r="146">
@@ -3113,7 +3113,7 @@
         <v>85</v>
       </c>
       <c r="E146" t="n">
-        <v>11500</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="147">
@@ -3132,7 +3132,7 @@
         <v>80</v>
       </c>
       <c r="E147" t="n">
-        <v>9500</v>
+        <v>65500</v>
       </c>
     </row>
     <row r="148">
@@ -3151,7 +3151,7 @@
         <v>75</v>
       </c>
       <c r="E148" t="n">
-        <v>7500</v>
+        <v>63500</v>
       </c>
     </row>
     <row r="149">
@@ -3170,7 +3170,7 @@
         <v>70</v>
       </c>
       <c r="E149" t="n">
-        <v>5500</v>
+        <v>61500</v>
       </c>
     </row>
     <row r="150">
@@ -3189,7 +3189,7 @@
         <v>65</v>
       </c>
       <c r="E150" t="n">
-        <v>3500</v>
+        <v>59500</v>
       </c>
     </row>
     <row r="151">
@@ -3208,7 +3208,7 @@
         <v>60</v>
       </c>
       <c r="E151" t="n">
-        <v>1500</v>
+        <v>57500</v>
       </c>
     </row>
     <row r="152">
@@ -3226,7 +3226,9 @@
       <c r="D152" t="n">
         <v>55</v>
       </c>
-      <c r="E152" t="inlineStr"/>
+      <c r="E152" t="n">
+        <v>55500</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -3243,7 +3245,9 @@
       <c r="D153" t="n">
         <v>50</v>
       </c>
-      <c r="E153" t="inlineStr"/>
+      <c r="E153" t="n">
+        <v>53500</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -3260,7 +3264,9 @@
       <c r="D154" t="n">
         <v>45</v>
       </c>
-      <c r="E154" t="inlineStr"/>
+      <c r="E154" t="n">
+        <v>51500</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -3277,7 +3283,9 @@
       <c r="D155" t="n">
         <v>40</v>
       </c>
-      <c r="E155" t="inlineStr"/>
+      <c r="E155" t="n">
+        <v>49500</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -3289,12 +3297,14 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>400</v>
+        <v>1520</v>
       </c>
       <c r="D156" t="n">
-        <v>35</v>
-      </c>
-      <c r="E156" t="inlineStr"/>
+        <v>175</v>
+      </c>
+      <c r="E156" t="n">
+        <v>47500</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -3306,12 +3316,14 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>360</v>
+        <v>1480</v>
       </c>
       <c r="D157" t="n">
-        <v>30</v>
-      </c>
-      <c r="E157" t="inlineStr"/>
+        <v>170</v>
+      </c>
+      <c r="E157" t="n">
+        <v>45500</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -3323,12 +3335,14 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>320</v>
+        <v>1440</v>
       </c>
       <c r="D158" t="n">
-        <v>25</v>
-      </c>
-      <c r="E158" t="inlineStr"/>
+        <v>165</v>
+      </c>
+      <c r="E158" t="n">
+        <v>43500</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -3340,12 +3354,14 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>280</v>
+        <v>1400</v>
       </c>
       <c r="D159" t="n">
-        <v>20</v>
-      </c>
-      <c r="E159" t="inlineStr"/>
+        <v>160</v>
+      </c>
+      <c r="E159" t="n">
+        <v>41500</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -3357,12 +3373,14 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>240</v>
+        <v>1360</v>
       </c>
       <c r="D160" t="n">
-        <v>15</v>
-      </c>
-      <c r="E160" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="E160" t="n">
+        <v>39500</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -3374,12 +3392,14 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>200</v>
+        <v>1320</v>
       </c>
       <c r="D161" t="n">
-        <v>10</v>
-      </c>
-      <c r="E161" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="E161" t="n">
+        <v>37500</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -3391,12 +3411,14 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>160</v>
+        <v>1280</v>
       </c>
       <c r="D162" t="n">
-        <v>5</v>
-      </c>
-      <c r="E162" t="inlineStr"/>
+        <v>145</v>
+      </c>
+      <c r="E162" t="n">
+        <v>35500</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -3408,10 +3430,14 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>120</v>
-      </c>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
+        <v>1240</v>
+      </c>
+      <c r="D163" t="n">
+        <v>140</v>
+      </c>
+      <c r="E163" t="n">
+        <v>33500</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -3423,10 +3449,14 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>80</v>
-      </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
+        <v>1200</v>
+      </c>
+      <c r="D164" t="n">
+        <v>135</v>
+      </c>
+      <c r="E164" t="n">
+        <v>31500</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -3438,10 +3468,14 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>40</v>
-      </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
+        <v>1160</v>
+      </c>
+      <c r="D165" t="n">
+        <v>130</v>
+      </c>
+      <c r="E165" t="n">
+        <v>29500</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -3452,9 +3486,15 @@
           <t>Thursday - for Friday (mg):</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
+      <c r="C166" t="n">
+        <v>1120</v>
+      </c>
+      <c r="D166" t="n">
+        <v>125</v>
+      </c>
+      <c r="E166" t="n">
+        <v>27500</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -3465,9 +3505,15 @@
           <t>Friday - for Saturday (mg):</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
+      <c r="C167" t="n">
+        <v>1080</v>
+      </c>
+      <c r="D167" t="n">
+        <v>120</v>
+      </c>
+      <c r="E167" t="n">
+        <v>25500</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -3478,9 +3524,15 @@
           <t>Saturday - for Sunday (mg):</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
+      <c r="C168" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D168" t="n">
+        <v>115</v>
+      </c>
+      <c r="E168" t="n">
+        <v>23500</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -3491,9 +3543,15 @@
           <t>Sunday - for Monday (mg):</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
+      <c r="C169" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D169" t="n">
+        <v>110</v>
+      </c>
+      <c r="E169" t="n">
+        <v>21500</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -3504,9 +3562,15 @@
           <t>Monday - for Tuesday (mg):</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+      <c r="C170" t="n">
+        <v>960</v>
+      </c>
+      <c r="D170" t="n">
+        <v>105</v>
+      </c>
+      <c r="E170" t="n">
+        <v>19500</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -3517,9 +3581,15 @@
           <t>Tuesday - for Wednesday (mg):</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+      <c r="C171" t="n">
+        <v>920</v>
+      </c>
+      <c r="D171" t="n">
+        <v>100</v>
+      </c>
+      <c r="E171" t="n">
+        <v>17500</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -3530,9 +3600,15 @@
           <t>Wednesday - for Thursday (mg):</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="C172" t="n">
+        <v>880</v>
+      </c>
+      <c r="D172" t="n">
+        <v>95</v>
+      </c>
+      <c r="E172" t="n">
+        <v>15500</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -3543,9 +3619,15 @@
           <t>Thursday - for Friday (mg):</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+      <c r="C173" t="n">
+        <v>840</v>
+      </c>
+      <c r="D173" t="n">
+        <v>90</v>
+      </c>
+      <c r="E173" t="n">
+        <v>13500</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -3556,9 +3638,15 @@
           <t>Friday - for Saturday (mg):</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+      <c r="C174" t="n">
+        <v>800</v>
+      </c>
+      <c r="D174" t="n">
+        <v>85</v>
+      </c>
+      <c r="E174" t="n">
+        <v>11500</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -3569,9 +3657,15 @@
           <t>Saturday - for Sunday (mg):</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+      <c r="C175" t="n">
+        <v>760</v>
+      </c>
+      <c r="D175" t="n">
+        <v>80</v>
+      </c>
+      <c r="E175" t="n">
+        <v>9500</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -3579,12 +3673,2007 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Sunday - for nan (mg):</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>720</v>
+      </c>
+      <c r="D176" t="n">
+        <v>75</v>
+      </c>
+      <c r="E176" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>680</v>
+      </c>
+      <c r="D177" t="n">
+        <v>70</v>
+      </c>
+      <c r="E177" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>640</v>
+      </c>
+      <c r="D178" t="n">
+        <v>65</v>
+      </c>
+      <c r="E178" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>1720</v>
+      </c>
+      <c r="D179" t="n">
+        <v>200</v>
+      </c>
+      <c r="E179" t="n">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>1680</v>
+      </c>
+      <c r="D180" t="n">
+        <v>195</v>
+      </c>
+      <c r="E180" t="n">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>1640</v>
+      </c>
+      <c r="D181" t="n">
+        <v>190</v>
+      </c>
+      <c r="E181" t="n">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>45969</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D182" t="n">
+        <v>185</v>
+      </c>
+      <c r="E182" t="n">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>45970</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>1560</v>
+      </c>
+      <c r="D183" t="n">
+        <v>180</v>
+      </c>
+      <c r="E183" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D184" t="n">
+        <v>175</v>
+      </c>
+      <c r="E184" t="n">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1480</v>
+      </c>
+      <c r="D185" t="n">
+        <v>170</v>
+      </c>
+      <c r="E185" t="n">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D186" t="n">
+        <v>165</v>
+      </c>
+      <c r="E186" t="n">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D187" t="n">
+        <v>160</v>
+      </c>
+      <c r="E187" t="n">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D188" t="n">
+        <v>155</v>
+      </c>
+      <c r="E188" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>1320</v>
+      </c>
+      <c r="D189" t="n">
+        <v>150</v>
+      </c>
+      <c r="E189" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D190" t="n">
+        <v>145</v>
+      </c>
+      <c r="E190" t="n">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D191" t="n">
+        <v>140</v>
+      </c>
+      <c r="E191" t="n">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D192" t="n">
+        <v>135</v>
+      </c>
+      <c r="E192" t="n">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>1160</v>
+      </c>
+      <c r="D193" t="n">
+        <v>130</v>
+      </c>
+      <c r="E193" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>1120</v>
+      </c>
+      <c r="D194" t="n">
+        <v>125</v>
+      </c>
+      <c r="E194" t="n">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>1080</v>
+      </c>
+      <c r="D195" t="n">
+        <v>120</v>
+      </c>
+      <c r="E195" t="n">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>45983</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D196" t="n">
+        <v>115</v>
+      </c>
+      <c r="E196" t="n">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D197" t="n">
+        <v>110</v>
+      </c>
+      <c r="E197" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>960</v>
+      </c>
+      <c r="D198" t="n">
+        <v>105</v>
+      </c>
+      <c r="E198" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>920</v>
+      </c>
+      <c r="D199" t="n">
+        <v>100</v>
+      </c>
+      <c r="E199" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>880</v>
+      </c>
+      <c r="D200" t="n">
+        <v>95</v>
+      </c>
+      <c r="E200" t="n">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>840</v>
+      </c>
+      <c r="D201" t="n">
+        <v>90</v>
+      </c>
+      <c r="E201" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>800</v>
+      </c>
+      <c r="D202" t="n">
+        <v>85</v>
+      </c>
+      <c r="E202" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>760</v>
+      </c>
+      <c r="D203" t="n">
+        <v>80</v>
+      </c>
+      <c r="E203" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>720</v>
+      </c>
+      <c r="D204" t="n">
+        <v>75</v>
+      </c>
+      <c r="E204" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>680</v>
+      </c>
+      <c r="D205" t="n">
+        <v>70</v>
+      </c>
+      <c r="E205" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>1760</v>
+      </c>
+      <c r="D206" t="n">
+        <v>205</v>
+      </c>
+      <c r="E206" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>1720</v>
+      </c>
+      <c r="D207" t="n">
+        <v>200</v>
+      </c>
+      <c r="E207" t="n">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>1680</v>
+      </c>
+      <c r="D208" t="n">
+        <v>195</v>
+      </c>
+      <c r="E208" t="n">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>1640</v>
+      </c>
+      <c r="D209" t="n">
+        <v>190</v>
+      </c>
+      <c r="E209" t="n">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>45997</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D210" t="n">
+        <v>185</v>
+      </c>
+      <c r="E210" t="n">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>45998</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>1560</v>
+      </c>
+      <c r="D211" t="n">
+        <v>180</v>
+      </c>
+      <c r="E211" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D212" t="n">
+        <v>175</v>
+      </c>
+      <c r="E212" t="n">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>1480</v>
+      </c>
+      <c r="D213" t="n">
+        <v>170</v>
+      </c>
+      <c r="E213" t="n">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D214" t="n">
+        <v>165</v>
+      </c>
+      <c r="E214" t="n">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D215" t="n">
+        <v>160</v>
+      </c>
+      <c r="E215" t="n">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>2480</v>
+      </c>
+      <c r="D216" t="n">
+        <v>295</v>
+      </c>
+      <c r="E216" t="n">
+        <v>96000</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>46004</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>2440</v>
+      </c>
+      <c r="D217" t="n">
+        <v>290</v>
+      </c>
+      <c r="E217" t="n">
+        <v>94000</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>46005</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D218" t="n">
+        <v>285</v>
+      </c>
+      <c r="E218" t="n">
+        <v>92000</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>2360</v>
+      </c>
+      <c r="D219" t="n">
+        <v>280</v>
+      </c>
+      <c r="E219" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>2320</v>
+      </c>
+      <c r="D220" t="n">
+        <v>275</v>
+      </c>
+      <c r="E220" t="n">
+        <v>88000</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>2280</v>
+      </c>
+      <c r="D221" t="n">
+        <v>270</v>
+      </c>
+      <c r="E221" t="n">
+        <v>86000</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>2240</v>
+      </c>
+      <c r="D222" t="n">
+        <v>265</v>
+      </c>
+      <c r="E222" t="n">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D223" t="n">
+        <v>260</v>
+      </c>
+      <c r="E223" t="n">
+        <v>82000</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46011</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>2160</v>
+      </c>
+      <c r="D224" t="n">
+        <v>255</v>
+      </c>
+      <c r="E224" t="n">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>2120</v>
+      </c>
+      <c r="D225" t="n">
+        <v>250</v>
+      </c>
+      <c r="E225" t="n">
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>2080</v>
+      </c>
+      <c r="D226" t="n">
+        <v>245</v>
+      </c>
+      <c r="E226" t="n">
+        <v>76000</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D227" t="n">
+        <v>240</v>
+      </c>
+      <c r="E227" t="n">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D228" t="n">
+        <v>235</v>
+      </c>
+      <c r="E228" t="n">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>1960</v>
+      </c>
+      <c r="D229" t="n">
+        <v>230</v>
+      </c>
+      <c r="E229" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>1920</v>
+      </c>
+      <c r="D230" t="n">
+        <v>225</v>
+      </c>
+      <c r="E230" t="n">
+        <v>68000</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46018</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>1880</v>
+      </c>
+      <c r="D231" t="n">
+        <v>220</v>
+      </c>
+      <c r="E231" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46019</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>1840</v>
+      </c>
+      <c r="D232" t="n">
+        <v>215</v>
+      </c>
+      <c r="E232" t="n">
+        <v>64000</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D233" t="n">
+        <v>210</v>
+      </c>
+      <c r="E233" t="n">
+        <v>62000</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1760</v>
+      </c>
+      <c r="D234" t="n">
+        <v>205</v>
+      </c>
+      <c r="E234" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>1720</v>
+      </c>
+      <c r="D235" t="n">
+        <v>200</v>
+      </c>
+      <c r="E235" t="n">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>1680</v>
+      </c>
+      <c r="D236" t="n">
+        <v>195</v>
+      </c>
+      <c r="E236" t="n">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>1640</v>
+      </c>
+      <c r="D237" t="n">
+        <v>190</v>
+      </c>
+      <c r="E237" t="n">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46025</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D238" t="n">
+        <v>185</v>
+      </c>
+      <c r="E238" t="n">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46026</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>1560</v>
+      </c>
+      <c r="D239" t="n">
+        <v>180</v>
+      </c>
+      <c r="E239" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D240" t="n">
+        <v>175</v>
+      </c>
+      <c r="E240" t="n">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>1480</v>
+      </c>
+      <c r="D241" t="n">
+        <v>170</v>
+      </c>
+      <c r="E241" t="n">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D242" t="n">
+        <v>165</v>
+      </c>
+      <c r="E242" t="n">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D243" t="n">
+        <v>160</v>
+      </c>
+      <c r="E243" t="n">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D244" t="n">
+        <v>155</v>
+      </c>
+      <c r="E244" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46032</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>1320</v>
+      </c>
+      <c r="D245" t="n">
+        <v>150</v>
+      </c>
+      <c r="E245" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D246" t="n">
+        <v>145</v>
+      </c>
+      <c r="E246" t="n">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D247" t="n">
+        <v>140</v>
+      </c>
+      <c r="E247" t="n">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D248" t="n">
+        <v>135</v>
+      </c>
+      <c r="E248" t="n">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>1160</v>
+      </c>
+      <c r="D249" t="n">
+        <v>130</v>
+      </c>
+      <c r="E249" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>1120</v>
+      </c>
+      <c r="D250" t="n">
+        <v>125</v>
+      </c>
+      <c r="E250" t="n">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>1080</v>
+      </c>
+      <c r="D251" t="n">
+        <v>120</v>
+      </c>
+      <c r="E251" t="n">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46039</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D252" t="n">
+        <v>115</v>
+      </c>
+      <c r="E252" t="n">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46040</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D253" t="n">
+        <v>110</v>
+      </c>
+      <c r="E253" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>960</v>
+      </c>
+      <c r="D254" t="n">
+        <v>105</v>
+      </c>
+      <c r="E254" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>920</v>
+      </c>
+      <c r="D255" t="n">
+        <v>100</v>
+      </c>
+      <c r="E255" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>880</v>
+      </c>
+      <c r="D256" t="n">
+        <v>95</v>
+      </c>
+      <c r="E256" t="n">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>840</v>
+      </c>
+      <c r="D257" t="n">
+        <v>90</v>
+      </c>
+      <c r="E257" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>800</v>
+      </c>
+      <c r="D258" t="n">
+        <v>85</v>
+      </c>
+      <c r="E258" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46046</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>760</v>
+      </c>
+      <c r="D259" t="n">
+        <v>80</v>
+      </c>
+      <c r="E259" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46047</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>720</v>
+      </c>
+      <c r="D260" t="n">
+        <v>75</v>
+      </c>
+      <c r="E260" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>680</v>
+      </c>
+      <c r="D261" t="n">
+        <v>70</v>
+      </c>
+      <c r="E261" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>640</v>
+      </c>
+      <c r="D262" t="n">
+        <v>65</v>
+      </c>
+      <c r="E262" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>600</v>
+      </c>
+      <c r="D263" t="n">
+        <v>60</v>
+      </c>
+      <c r="E263" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>560</v>
+      </c>
+      <c r="D264" t="n">
+        <v>55</v>
+      </c>
+      <c r="E264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>520</v>
+      </c>
+      <c r="D265" t="n">
+        <v>50</v>
+      </c>
+      <c r="E265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>480</v>
+      </c>
+      <c r="D266" t="n">
+        <v>45</v>
+      </c>
+      <c r="E266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>440</v>
+      </c>
+      <c r="D267" t="n">
+        <v>40</v>
+      </c>
+      <c r="E267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>400</v>
+      </c>
+      <c r="D268" t="n">
+        <v>35</v>
+      </c>
+      <c r="E268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>360</v>
+      </c>
+      <c r="D269" t="n">
+        <v>30</v>
+      </c>
+      <c r="E269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>320</v>
+      </c>
+      <c r="D270" t="n">
+        <v>25</v>
+      </c>
+      <c r="E270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>280</v>
+      </c>
+      <c r="D271" t="n">
+        <v>20</v>
+      </c>
+      <c r="E271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>240</v>
+      </c>
+      <c r="D272" t="n">
+        <v>15</v>
+      </c>
+      <c r="E272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46060</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>200</v>
+      </c>
+      <c r="D273" t="n">
+        <v>10</v>
+      </c>
+      <c r="E273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>46061</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>160</v>
+      </c>
+      <c r="D274" t="n">
+        <v>5</v>
+      </c>
+      <c r="E274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>120</v>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>80</v>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>40</v>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Thursday - for Friday (mg):</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Friday - for Saturday (mg):</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>46067</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Saturday - for Sunday (mg):</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>46068</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Sunday - for Monday (mg):</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Monday - for Tuesday (mg):</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Tuesday - for Wednesday (mg):</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Wednesday - for Thursday (mg):</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Thursday - for nan (mg):</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
